--- a/OUTPUT/reverse_Q7CFV3_Yersinia_pestis_biovar_Microtus_str__91001.xlsx
+++ b/OUTPUT/reverse_Q7CFV3_Yersinia_pestis_biovar_Microtus_str__91001.xlsx
@@ -477,16 +477,16 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>CAA</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>TTG</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>AAC</t>
-        </is>
-      </c>
       <c r="G2" t="n">
-        <v>0.995</v>
+        <v>0.9948020791683326</v>
       </c>
     </row>
     <row r="3">
@@ -506,16 +506,16 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>GAT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>ATC</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>TAG</t>
-        </is>
-      </c>
       <c r="G3" t="n">
-        <v>0.995</v>
+        <v>0.9948020791683326</v>
       </c>
     </row>
     <row r="4">
@@ -535,16 +535,16 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>TGA</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>TCA</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>AGT</t>
-        </is>
-      </c>
       <c r="G4" t="n">
-        <v>0.995</v>
+        <v>0.9948020791683326</v>
       </c>
     </row>
     <row r="5">
@@ -564,16 +564,16 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>GTG</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>CAC</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>GTG</t>
-        </is>
-      </c>
       <c r="G5" t="n">
-        <v>0.995</v>
+        <v>0.9948020791683326</v>
       </c>
     </row>
     <row r="6">
@@ -593,16 +593,16 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>TG</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="7">
@@ -622,16 +622,16 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="8">
@@ -651,16 +651,16 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>TG</t>
-        </is>
-      </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="9">
@@ -680,16 +680,16 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="10">
@@ -709,16 +709,16 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="11">
@@ -738,16 +738,16 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="12">
@@ -767,16 +767,16 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>TC</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>AG</t>
-        </is>
-      </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="13">
@@ -796,16 +796,16 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>TC</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>AG</t>
-        </is>
-      </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="14">
@@ -825,16 +825,16 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>GG</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>GG</t>
-        </is>
-      </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="15">
@@ -854,16 +854,16 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>GG</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>GG</t>
-        </is>
-      </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="16">
@@ -883,16 +883,16 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>TG</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>GT</t>
-        </is>
-      </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="17">
@@ -912,16 +912,16 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>TG</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>GT</t>
-        </is>
-      </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="18">
@@ -946,11 +946,11 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CG</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="19">
@@ -970,16 +970,16 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>TG</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>GT</t>
-        </is>
-      </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="20">
@@ -999,16 +999,16 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>TG</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>GT</t>
-        </is>
-      </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
   </sheetData>
